--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Make product web by gemini\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05CC33A-D02E-4B9F-B2AE-E2C454A38C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA1B911-B8B2-481F-A0A7-66F8820D064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{916ECA9C-5D45-4535-AC7C-19EB97992461}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="88">
   <si>
     <t>id</t>
   </si>
@@ -288,13 +288,25 @@
   </si>
   <si>
     <t>media/Acquy_YT5_3_2.jpg, media/Acquy_YT5_3_1.jpg</t>
+  </si>
+  <si>
+    <t>Sạc Dự Phòng 15.000 mah</t>
+  </si>
+  <si>
+    <t>Sạc dự phòng 15.000 mah\n Lõi pin: LG50LT, LGM52VT, Samsung50E\n Dung lượng: 15.000 mah\n Công suất 22.5W\n Cổng sạc input: Type C\n Cổng sạc Output: USB, Type C\n Chất liệu: Vỏ nhôm và nhựa ABS\n Kích thước: 80x56x24mm\n Giá:350K</t>
+  </si>
+  <si>
+    <t>media/sdp_15000mah.jpg</t>
+  </si>
+  <si>
+    <t>media/sdp_15000mah.jpg, media/sdp_15000mah_1.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -324,7 +336,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -347,16 +359,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -693,17 +719,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA99146E-47F7-4784-ACAB-DA386730C5D0}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="255.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="139.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="139.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.4" thickBot="1">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.4" thickBot="1">
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -743,7 +769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.4" thickBot="1">
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -763,7 +789,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.4" thickBot="1">
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -783,7 +809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.4" thickBot="1">
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -803,7 +829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.4" thickBot="1">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -823,7 +849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.4" thickBot="1">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -843,7 +869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.4" thickBot="1">
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -863,7 +889,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.4" thickBot="1">
+    <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -883,7 +909,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.4" thickBot="1">
+    <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -903,7 +929,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.4" thickBot="1">
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>20</v>
       </c>
@@ -923,7 +949,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.4" thickBot="1">
+    <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>21</v>
       </c>
@@ -943,7 +969,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.4" thickBot="1">
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>22</v>
       </c>
@@ -963,7 +989,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.4" thickBot="1">
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>23</v>
       </c>
@@ -983,7 +1009,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.4" thickBot="1">
+    <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>24</v>
       </c>
@@ -1003,7 +1029,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.4" thickBot="1">
+    <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>25</v>
       </c>
@@ -1023,7 +1049,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="14.4" thickBot="1">
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>30</v>
       </c>
@@ -1043,7 +1069,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.4" thickBot="1">
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>31</v>
       </c>
@@ -1063,7 +1089,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.4" thickBot="1">
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>32</v>
       </c>
@@ -1083,7 +1109,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.4" thickBot="1">
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>33</v>
       </c>
@@ -1103,7 +1129,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.4" thickBot="1">
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>34</v>
       </c>
@@ -1123,7 +1149,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="14.4" thickBot="1">
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>35</v>
       </c>
@@ -1141,6 +1167,26 @@
       </c>
       <c r="F22" s="2" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>10</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Make product web by gemini\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huu Thien\Documents\GitHub\Battery-Workshop-By-Thien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA1B911-B8B2-481F-A0A7-66F8820D064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F70C32-C69C-49B5-B7F8-C84C85EB2226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{916ECA9C-5D45-4535-AC7C-19EB97992461}"/>
   </bookViews>
@@ -293,13 +293,13 @@
     <t>Sạc Dự Phòng 15.000 mah</t>
   </si>
   <si>
-    <t>Sạc dự phòng 15.000 mah\n Lõi pin: LG50LT, LGM52VT, Samsung50E\n Dung lượng: 15.000 mah\n Công suất 22.5W\n Cổng sạc input: Type C\n Cổng sạc Output: USB, Type C\n Chất liệu: Vỏ nhôm và nhựa ABS\n Kích thước: 80x56x24mm\n Giá:350K</t>
-  </si>
-  <si>
     <t>media/sdp_15000mah.jpg</t>
   </si>
   <si>
     <t>media/sdp_15000mah.jpg, media/sdp_15000mah_1.jpg</t>
+  </si>
+  <si>
+    <t>Sạc dự phòng 15.000 mah\n Lõi pin: LG50LT, LGM52VT, Samsung50E\n Dung lượng: 15.000 mah\n Công suất 22.5W với IC SW6236 ngon hơn những loại phổ thông IP5356\n Cổng sạc input: Type C, Lightning \n Cổng sạc Output: USB, Type C\n Chất liệu: Vỏ nhựa ABS\n Kích thước: 80x56x24mm\n Giá:350K</t>
   </si>
 </sst>
 </file>
@@ -382,7 +382,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1180,13 +1180,13 @@
         <v>84</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huu Thien\Documents\GitHub\Battery-Workshop-By-Thien\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F70C32-C69C-49B5-B7F8-C84C85EB2226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E660B34-13AD-4207-822A-0ED98A848107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{916ECA9C-5D45-4535-AC7C-19EB97992461}"/>
   </bookViews>
@@ -299,7 +299,7 @@
     <t>media/sdp_15000mah.jpg, media/sdp_15000mah_1.jpg</t>
   </si>
   <si>
-    <t>Sạc dự phòng 15.000 mah\n Lõi pin: LG50LT, LGM52VT, Samsung50E\n Dung lượng: 15.000 mah\n Công suất 22.5W với IC SW6236 ngon hơn những loại phổ thông IP5356\n Cổng sạc input: Type C, Lightning \n Cổng sạc Output: USB, Type C\n Chất liệu: Vỏ nhựa ABS\n Kích thước: 80x56x24mm\n Giá:350K</t>
+    <t>Sạc dự phòng 15.000 mah\n Lõi pin: LG50LT, LGM52VT, Samsung50E\n Dung lượng: 15.000 mah\n Công suất 22.5W với IC SW6236 ngon hơn những loại phổ thông IP5356\n Cổng sạc input: Type C, Lightning \n Cổng sạc Output: USB, Type C\n Chất liệu: Vỏ nhựa ABS\n Kích thước: 110x70x30mm\n Giá:350K</t>
   </si>
 </sst>
 </file>
